--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R749cffc6ee494432"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Ree45017c89ce4ed4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -371,7 +371,7 @@
         <x:v>核心操作链</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>排序申请；规范化URL；重建UTM；识别现网占用；处置短码；生成映射；汇总迁移</x:v>
+        <x:v>排序申请；规整URL；重建UTM；识别现网占用；处置短码；生成映射；汇总迁移</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
@@ -384,10 +384,10 @@
     </x:row>
     <x:row r="11" ht="32" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>短码裁决</x:v>
+        <x:v>短码处置</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>按run_at_utc区分占用和回收，复用需要团队与规范化目标同时一致，冲突使用最小可用后缀</x:v>
+        <x:v>按run_at_utc区分占用和收回，沿用需要团队与规整后目标同时一致，冲突使用最小可用后缀</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="46" customHeight="1">
@@ -408,10 +408,10 @@
     </x:row>
     <x:row r="14" ht="32" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>汇总合同</x:v>
+        <x:v>迁移汇总</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>migration_summary.json从处置记录和路由映射复算主要迁移分支</x:v>
+        <x:v>migration_summary.json从处置记录和路由映射汇总主要处置分支</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="32" customHeight="1">
@@ -419,7 +419,7 @@
         <x:v>完成条件</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>Node.js入口正常结束，四份交付可读，request_id与slug能够跨文件追溯，汇总数量闭合</x:v>
+        <x:v>Node.js入口正常结束，四份交付可读，request_id与slug能够跨文件对应，汇总数量相互一致</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="32" customHeight="1">
@@ -427,7 +427,7 @@
         <x:v>可验证点</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
-        <x:v>协议、域名、query键、UTM、短码状态、处置身份和汇总均能从输入复算</x:v>
+        <x:v>协议、域名、query字段、UTM、短码状态、处置结论和汇总均能从输入对应</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="32" customHeight="1">

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Ree45017c89ce4ed4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Re1a86264e60f47d3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -339,7 +339,7 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>脱敏活动申请、增长平台迁移政策和现网短码快照</x:v>
+        <x:v>本次业务输入包含活动申请、增长平台迁移政策和现网短码快照</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
@@ -376,66 +376,90 @@
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
       <x:c r="A10" s="7" t="str">
-        <x:v>地址政策</x:v>
+        <x:v>业务目标</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>HTTPS与域名、保留参数和UTM字段均由migration_policy.json读取</x:v>
+        <x:v>为增长平台迁移短链路由，向路由服务交付映射，向运营团队交付逐条处置记录，向发布负责人交付迁移汇总</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="32" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>短码处置</x:v>
+        <x:v>交付要求</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>按run_at_utc区分占用和收回，沿用需要团队与规整后目标同时一致，冲突使用最小可用后缀</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="46" customHeight="1">
+        <x:v>完成程序、路由映射、申请处置记录和迁移汇总使用固定相对路径，request_id与slug能够跨交付对应</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="32" customHeight="1">
       <x:c r="A12" s="7" t="str">
-        <x:v>申请覆盖</x:v>
+        <x:v>软件步骤</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>shortlink_requests.csv中的每个request_id在transition_log.csv恰有一条处置</x:v>
+        <x:v>Node.js读取三份业务材料，规整地址与UTM参数，判断短码占用或收回状态，分配冲突后缀，再生成四份交付</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="32" customHeight="1">
       <x:c r="A13" s="7" t="str">
-        <x:v>路由导入</x:v>
+        <x:v>地址政策</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
-        <x:v>接纳申请进入redirect_map.jsonl，拒绝申请只保留在transition_log.csv</x:v>
+        <x:v>HTTPS与域名、保留参数和UTM字段均由migration_policy.json读取</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="32" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>迁移汇总</x:v>
+        <x:v>短码处置</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>migration_summary.json从处置记录和路由映射汇总主要处置分支</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="32" customHeight="1">
+        <x:v>按run_at_utc区分占用和收回，沿用需要团队与规整后目标同时一致，冲突使用最小可用后缀</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="46" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>申请覆盖</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>Node.js入口正常结束，四份交付可读，request_id与slug能够跨文件对应，汇总数量相互一致</x:v>
+        <x:v>shortlink_requests.csv中的每个request_id在transition_log.csv恰有一条处置</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="32" customHeight="1">
       <x:c r="A16" s="7" t="str">
-        <x:v>可验证点</x:v>
+        <x:v>路由导入</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
-        <x:v>协议、域名、query字段、UTM、短码状态、处置结论和汇总均能从输入对应</x:v>
+        <x:v>接纳申请进入redirect_map.jsonl，拒绝申请只保留在transition_log.csv</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="32" customHeight="1">
       <x:c r="A17" s="7" t="str">
+        <x:v>迁移汇总</x:v>
+      </x:c>
+      <x:c r="B17" s="7" t="str">
+        <x:v>migration_summary.json从处置记录和路由映射汇总主要处置分支</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="32" customHeight="1">
+      <x:c r="A18" s="7" t="str">
+        <x:v>完成条件</x:v>
+      </x:c>
+      <x:c r="B18" s="7" t="str">
+        <x:v>Node.js入口正常结束，四份交付可读，request_id与slug能够跨文件对应，汇总数量相互一致</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="32" customHeight="1">
+      <x:c r="A19" s="7" t="str">
+        <x:v>可验证点</x:v>
+      </x:c>
+      <x:c r="B19" s="7" t="str">
+        <x:v>协议、域名、query字段、UTM、短码状态、处置结论和汇总均能从本次业务输入对应</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="32" customHeight="1">
+      <x:c r="A20" s="7" t="str">
         <x:v>不适合作为评分点的内容</x:v>
       </x:c>
-      <x:c r="B17" s="7" t="str">
-        <x:v>函数拆分、内部容器、JSON键序、CSV引用符、本机路径和源码注释可以不同</x:v>
+      <x:c r="B20" s="7" t="str">
+        <x:v>实现边界限于业务结果；函数拆分、内部容器、JSON键序、CSV引用符、本机路径和源码注释可以不同</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Re1a86264e60f47d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rf2cebe6ca317497f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -342,25 +342,25 @@
         <x:v>本次业务输入包含活动申请、增长平台迁移政策和现网短码快照</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="32" customHeight="1">
+    <x:row r="6" ht="46" customHeight="1">
       <x:c r="A6" s="7" t="str">
-        <x:v>输入获取方式</x:v>
+        <x:v>业务输入</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>解压输入数据包后从input_data读取本地材料</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="46" customHeight="1">
+        <x:v>shortlink_requests.csv；migration_policy.json；existing_slugs.json；starter/build_redirect_map.mjs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
       <x:c r="A7" s="7" t="str">
-        <x:v>原始输入文件</x:v>
+        <x:v>迁移目标</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>shortlink_requests.csv；migration_policy.json；existing_slugs.json；starter/build_redirect_map.mjs</x:v>
+        <x:v>为增长平台迁移短链路由，向路由服务交付映射，向运营团队交付逐条处置记录，向发布负责人交付迁移汇总</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="60" customHeight="1">
       <x:c r="A8" s="7" t="str">
-        <x:v>目标输出文件</x:v>
+        <x:v>交付文件</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
         <x:v>output/src/build_redirect_map.mjs；output/redirect_map.jsonl；output/transition_log.csv；output/migration_summary.json</x:v>
@@ -368,98 +368,74 @@
     </x:row>
     <x:row r="9" ht="32" customHeight="1">
       <x:c r="A9" s="7" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>Node.js步骤</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>排序申请；规整URL；重建UTM；识别现网占用；处置短码；生成映射；汇总迁移</x:v>
+        <x:v>读取申请和政策；规整URL；重建UTM；关联现网快照；判断短码状态；分配冲突后缀；写出路由、处置和汇总</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
       <x:c r="A10" s="7" t="str">
-        <x:v>业务目标</x:v>
+        <x:v>地址政策</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>为增长平台迁移短链路由，向路由服务交付映射，向运营团队交付逐条处置记录，向发布负责人交付迁移汇总</x:v>
+        <x:v>HTTPS与域名、保留参数和UTM字段均由migration_policy.json读取</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="32" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>交付要求</x:v>
+        <x:v>短码处置</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>完成程序、路由映射、申请处置记录和迁移汇总使用固定相对路径，request_id与slug能够跨交付对应</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="32" customHeight="1">
+        <x:v>按run_at_utc区分占用和收回，沿用需要团队与规整后目标同时一致，冲突使用最小可用后缀</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="46" customHeight="1">
       <x:c r="A12" s="7" t="str">
-        <x:v>软件步骤</x:v>
+        <x:v>申请覆盖</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>Node.js读取三份业务材料，规整地址与UTM参数，判断短码占用或收回状态，分配冲突后缀，再生成四份交付</x:v>
+        <x:v>shortlink_requests.csv中的每个request_id在transition_log.csv恰有一条处置</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="32" customHeight="1">
       <x:c r="A13" s="7" t="str">
-        <x:v>地址政策</x:v>
+        <x:v>路由导入</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
-        <x:v>HTTPS与域名、保留参数和UTM字段均由migration_policy.json读取</x:v>
+        <x:v>接纳申请进入redirect_map.jsonl，拒绝申请只保留在transition_log.csv</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="32" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>短码处置</x:v>
+        <x:v>迁移汇总</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>按run_at_utc区分占用和收回，沿用需要团队与规整后目标同时一致，冲突使用最小可用后缀</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="46" customHeight="1">
+        <x:v>migration_summary.json从处置记录和路由映射汇总主要处置分支</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="32" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>申请覆盖</x:v>
+        <x:v>材料边界</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>shortlink_requests.csv中的每个request_id在transition_log.csv恰有一条处置</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="32" customHeight="1">
+        <x:v>现网短码作为只读快照参与裁决，程序和三份业务结果写入output</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="46" customHeight="1">
       <x:c r="A16" s="7" t="str">
-        <x:v>路由导入</x:v>
+        <x:v>结果对账</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
-        <x:v>接纳申请进入redirect_map.jsonl，拒绝申请只保留在transition_log.csv</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="32" customHeight="1">
+        <x:v>request_id连接申请、处置和路由，slug连接现网快照、处置记录和最终映射，汇总数量由处置记录与路由映射复算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="46" customHeight="1">
       <x:c r="A17" s="7" t="str">
-        <x:v>迁移汇总</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B17" s="7" t="str">
-        <x:v>migration_summary.json从处置记录和路由映射汇总主要处置分支</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="32" customHeight="1">
-      <x:c r="A18" s="7" t="str">
-        <x:v>完成条件</x:v>
-      </x:c>
-      <x:c r="B18" s="7" t="str">
-        <x:v>Node.js入口正常结束，四份交付可读，request_id与slug能够跨文件对应，汇总数量相互一致</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="32" customHeight="1">
-      <x:c r="A19" s="7" t="str">
-        <x:v>可验证点</x:v>
-      </x:c>
-      <x:c r="B19" s="7" t="str">
-        <x:v>协议、域名、query字段、UTM、短码状态、处置结论和汇总均能从本次业务输入对应</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="32" customHeight="1">
-      <x:c r="A20" s="7" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
-      </x:c>
-      <x:c r="B20" s="7" t="str">
-        <x:v>实现边界限于业务结果；函数拆分、内部容器、JSON键序、CSV引用符、本机路径和源码注释可以不同</x:v>
+        <x:v>函数拆分、内部容器、JSON键序、CSV引用符、本机路径和源码注释可以不同；政策字段、业务主键、交付路径与跨文件关系保持一致</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rf2cebe6ca317497f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R471f19006f264dc0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -318,124 +318,108 @@
         <x:v>node_shortlink_migration_routing_review</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="32" customHeight="1">
+    <x:row r="3" ht="46" customHeight="1">
       <x:c r="A3" s="7" t="str">
-        <x:v>主软件</x:v>
+        <x:v>短链迁移职责</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>Node.js</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="32" customHeight="1">
+        <x:v>迁移工程师把活动申请、迁移政策和现网短码合并成可导入的路由映射，并把拒绝、沿用、收回和冲突分配写进申请处置记录。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="60" customHeight="1">
       <x:c r="A4" s="7" t="str">
-        <x:v>辅助工具</x:v>
+        <x:v>本次业务输入</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>PowerShell或系统终端、CSV与JSON查看器</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="32" customHeight="1">
+        <x:v>shortlink_requests.csv保存活动申请与优先级；migration_policy.json规定地址、UTM和短码政策；existing_slugs.json是现网短码快照；starter/build_redirect_map.mjs是待完成程序。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="46" customHeight="1">
       <x:c r="A5" s="7" t="str">
-        <x:v>输入来源</x:v>
+        <x:v>业务消费者</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>本次业务输入包含活动申请、增长平台迁移政策和现网短码快照</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="46" customHeight="1">
+        <x:v>路由服务导入redirect_map.jsonl；活动运营查看transition_log.csv追踪申请；发布负责人使用migration_summary.json安排换批。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="60" customHeight="1">
       <x:c r="A6" s="7" t="str">
-        <x:v>业务输入</x:v>
+        <x:v>Node.js处理入口</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>shortlink_requests.csv；migration_policy.json；existing_slugs.json；starter/build_redirect_map.mjs</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="32" customHeight="1">
+        <x:v>在输入包解压目录执行node output/src/build_redirect_map.mjs input_data output。程序读取本地CSV与JSON，使用Node.js自带URL、文件系统和路径接口，业务结果写入output。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="46" customHeight="1">
       <x:c r="A7" s="7" t="str">
-        <x:v>迁移目标</x:v>
+        <x:v>落地地址规整</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>为增长平台迁移短链路由，向路由服务交付映射，向运营团队交付逐条处置记录，向发布负责人交付迁移汇总</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="60" customHeight="1">
+        <x:v>仅接纳政策允许的HTTPS域名；移除片段和未保留参数；按migration_policy.json重建UTM字段，要求规整结果可直接作为路由目标。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="46" customHeight="1">
       <x:c r="A8" s="7" t="str">
-        <x:v>交付文件</x:v>
+        <x:v>申请处理顺序</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>output/src/build_redirect_map.mjs；output/redirect_map.jsonl；output/transition_log.csv；output/migration_summary.json</x:v>
+        <x:v>先按priority降序，再按requested_at_utc和request_id升序处理申请，使同批短码冲突有稳定的业务先后。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="32" customHeight="1">
       <x:c r="A9" s="7" t="str">
-        <x:v>Node.js步骤</x:v>
+        <x:v>短码沿用与收回</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>读取申请和政策；规整URL；重建UTM；关联现网快照；判断短码状态；分配冲突后缀；写出路由、处置和汇总</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="32" customHeight="1">
+        <x:v>以run_at_utc判断现网短码是否仍占用；相同团队且目标一致时沿用活动短码；停用或已过期短码可以收回。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="46" customHeight="1">
       <x:c r="A10" s="7" t="str">
-        <x:v>地址政策</x:v>
+        <x:v>冲突后缀分配</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>HTTPS与域名、保留参数和UTM字段均由migration_policy.json读取</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="32" customHeight="1">
+        <x:v>现网占用或本批已分配造成冲突时，从migration_policy.json读取分隔符，选择最小可用两位数字后缀。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="46" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>短码处置</x:v>
+        <x:v>申请处置记录</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>按run_at_utc区分占用和收回，沿用需要团队与规整后目标同时一致，冲突使用最小可用后缀</x:v>
+        <x:v>shortlink_requests.csv中的每个request_id在transition_log.csv恰有一条记录，保留原申请短码、最终短码、处置类型、原因及现网状态。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="46" customHeight="1">
       <x:c r="A12" s="7" t="str">
-        <x:v>申请覆盖</x:v>
+        <x:v>路由映射边界</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>shortlink_requests.csv中的每个request_id在transition_log.csv恰有一条处置</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="32" customHeight="1">
+        <x:v>接纳申请进入redirect_map.jsonl，拒绝申请不进入路由映射；每行保存request_id、slug、团队、活动、目标地址、到期时间和处置类型。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="46" customHeight="1">
       <x:c r="A13" s="7" t="str">
-        <x:v>路由导入</x:v>
+        <x:v>迁移汇总口径</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
-        <x:v>接纳申请进入redirect_map.jsonl，拒绝申请只保留在transition_log.csv</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="32" customHeight="1">
+        <x:v>migration_summary.json从申请处置和路由映射汇总申请、接纳、拒绝、沿用、收回与冲突分配数量，status来自迁移政策。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="60" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>迁移汇总</x:v>
+        <x:v>交付目录</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>migration_summary.json从处置记录和路由映射汇总主要处置分支</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="32" customHeight="1">
+        <x:v>交付output/src/build_redirect_map.mjs、output/redirect_map.jsonl、output/transition_log.csv和output/migration_summary.json。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="46" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>材料边界</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>现网短码作为只读快照参与裁决，程序和三份业务结果写入output</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="46" customHeight="1">
-      <x:c r="A16" s="7" t="str">
-        <x:v>结果对账</x:v>
-      </x:c>
-      <x:c r="B16" s="7" t="str">
-        <x:v>request_id连接申请、处置和路由，slug连接现网快照、处置记录和最终映射，汇总数量由处置记录与路由映射复算</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="46" customHeight="1">
-      <x:c r="A17" s="7" t="str">
-        <x:v>实现边界</x:v>
-      </x:c>
-      <x:c r="B17" s="7" t="str">
-        <x:v>函数拆分、内部容器、JSON键序、CSV引用符、本机路径和源码注释可以不同；政策字段、业务主键、交付路径与跨文件关系保持一致</x:v>
+        <x:v>允许调整函数拆分、内部容器、JSON键序、CSV引用符、本机路径和源码注释；迁移政策、业务主键、交付路径及跨文件关系不得变化。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
